--- a/Data/input_GRID.xlsx
+++ b/Data/input_GRID.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ModellingRepos\VintageDemo\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D6239E6-1067-4E31-9E87-1BDA896BFCA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E8B950-75DD-466F-BC61-E1136D53EA66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,31 +48,6 @@
   </authors>
   <commentList>
     <comment ref="E3" authorId="0" shapeId="0" xr:uid="{20C43943-4B78-4790-AA82-441632017555}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Huang  Jiangyi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Mannually read from ONDP "Study Explorer": https://www.entsoe.eu/outlooks/offshore-hub/tyndp-ondp
-*Red values are intropolated</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AD3" authorId="0" shapeId="0" xr:uid="{99721743-FB1F-432D-B5B0-681A2059CD8C}">
       <text>
         <r>
           <rPr>
@@ -148,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11730" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11634" uniqueCount="89">
   <si>
     <t>FROM</t>
   </si>
@@ -845,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62038E97-233B-4D8D-9A57-141344E1B3B2}">
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AE59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -864,21 +839,20 @@
     <col min="22" max="22" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="F1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
         <v>84</v>
       </c>
@@ -924,11 +898,8 @@
       <c r="X2" t="s">
         <v>13</v>
       </c>
-      <c r="AD2" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>83</v>
       </c>
@@ -995,23 +966,8 @@
       <c r="X3" t="s">
         <v>5</v>
       </c>
-      <c r="Z3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD3" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1092,27 +1048,14 @@
         <f t="array" ref="X4">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N4)*('COST(R)'!$B$2:$B$2731=$O4)*('COST(R)'!$C$2:$C$2731=$P4)*('COST(R)'!$E$2:$E$2731=$Q4)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>352.42672762472449</v>
       </c>
-      <c r="Z4" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB4">
-        <v>2030</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD4" s="9"/>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="6"/>
-      <c r="AH4" s="5"/>
-      <c r="AI4" s="5"/>
-      <c r="AJ4" s="5"/>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1194,27 +1137,14 @@
         <f t="array" ref="X5">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N5)*('COST(R)'!$B$2:$B$2731=$O5)*('COST(R)'!$C$2:$C$2731=$P5)*('COST(R)'!$E$2:$E$2731=$Q5)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>500.74820791711772</v>
       </c>
-      <c r="Z5" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB5">
-        <v>2030</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD5" s="9"/>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="6"/>
-      <c r="AG5" s="6"/>
-      <c r="AH5" s="5"/>
-      <c r="AI5" s="5"/>
-      <c r="AJ5" s="5"/>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z5" s="6"/>
+      <c r="AA5" s="6"/>
+      <c r="AB5" s="6"/>
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="5"/>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>A5</f>
         <v>BE00</v>
@@ -1297,27 +1227,14 @@
         <f t="array" ref="X6">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N6)*('COST(R)'!$B$2:$B$2731=$O6)*('COST(R)'!$C$2:$C$2731=$P6)*('COST(R)'!$E$2:$E$2731=$Q6)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>492.78199498925989</v>
       </c>
-      <c r="Z6" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB6">
-        <v>2030</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD6" s="10"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="5"/>
-      <c r="AI6" s="5"/>
-      <c r="AJ6" s="5"/>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z6" s="6"/>
+      <c r="AA6" s="6"/>
+      <c r="AB6" s="6"/>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="5"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f t="shared" ref="A7:A9" si="2">A6</f>
         <v>BE00</v>
@@ -1400,27 +1317,14 @@
         <f t="array" ref="X7">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N7)*('COST(R)'!$B$2:$B$2731=$O7)*('COST(R)'!$C$2:$C$2731=$P7)*('COST(R)'!$E$2:$E$2731=$Q7)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>517.1042451889582</v>
       </c>
-      <c r="Z7" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB7">
-        <v>2030</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD7" s="9"/>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="5"/>
-      <c r="AI7" s="5"/>
-      <c r="AJ7" s="5"/>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="5"/>
+      <c r="AE7" s="5"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f t="shared" si="2"/>
         <v>BE00</v>
@@ -1503,27 +1407,14 @@
         <f t="array" ref="X8">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N8)*('COST(R)'!$B$2:$B$2731=$O8)*('COST(R)'!$C$2:$C$2731=$P8)*('COST(R)'!$E$2:$E$2731=$Q8)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>436.6230712505693</v>
       </c>
-      <c r="Z8" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB8">
-        <v>2030</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD8" s="10"/>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
-      <c r="AG8" s="6"/>
-      <c r="AH8" s="5"/>
-      <c r="AI8" s="5"/>
-      <c r="AJ8" s="5"/>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z8" s="6"/>
+      <c r="AA8" s="6"/>
+      <c r="AB8" s="6"/>
+      <c r="AC8" s="5"/>
+      <c r="AD8" s="5"/>
+      <c r="AE8" s="5"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f t="shared" si="2"/>
         <v>BE00</v>
@@ -1606,27 +1497,14 @@
         <f t="array" ref="X9">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N9)*('COST(R)'!$B$2:$B$2731=$O9)*('COST(R)'!$C$2:$C$2731=$P9)*('COST(R)'!$E$2:$E$2731=$Q9)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>352.42672762472449</v>
       </c>
-      <c r="Z9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB9">
-        <v>2030</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD9" s="9"/>
-      <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
-      <c r="AG9" s="6"/>
-      <c r="AH9" s="5"/>
-      <c r="AI9" s="5"/>
-      <c r="AJ9" s="5"/>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z9" s="6"/>
+      <c r="AA9" s="6"/>
+      <c r="AB9" s="6"/>
+      <c r="AC9" s="5"/>
+      <c r="AD9" s="5"/>
+      <c r="AE9" s="5"/>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1707,27 +1585,14 @@
         <f t="array" ref="X10">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N10)*('COST(R)'!$B$2:$B$2731=$O10)*('COST(R)'!$C$2:$C$2731=$P10)*('COST(R)'!$E$2:$E$2731=$Q10)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>500.74820791711772</v>
       </c>
-      <c r="Z10" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB10">
-        <v>2035</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD10" s="9"/>
-      <c r="AE10" s="6"/>
-      <c r="AF10" s="6"/>
-      <c r="AG10" s="6"/>
-      <c r="AH10" s="5"/>
-      <c r="AI10" s="5"/>
-      <c r="AJ10" s="5"/>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z10" s="6"/>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="5"/>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1809,27 +1674,14 @@
         <f t="array" ref="X11">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N11)*('COST(R)'!$B$2:$B$2731=$O11)*('COST(R)'!$C$2:$C$2731=$P11)*('COST(R)'!$E$2:$E$2731=$Q11)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>492.78199498925989</v>
       </c>
-      <c r="Z11" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB11">
-        <v>2035</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD11" s="9"/>
-      <c r="AE11" s="6"/>
-      <c r="AF11" s="6"/>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="5"/>
-      <c r="AI11" s="5"/>
-      <c r="AJ11" s="5"/>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="5"/>
+      <c r="AD11" s="5"/>
+      <c r="AE11" s="5"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>A11</f>
         <v>DE00</v>
@@ -1912,27 +1764,14 @@
         <f t="array" ref="X12">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N12)*('COST(R)'!$B$2:$B$2731=$O12)*('COST(R)'!$C$2:$C$2731=$P12)*('COST(R)'!$E$2:$E$2731=$Q12)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>517.1042451889582</v>
       </c>
-      <c r="Z12" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB12">
-        <v>2035</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD12" s="10"/>
-      <c r="AE12" s="6"/>
-      <c r="AF12" s="6"/>
-      <c r="AG12" s="6"/>
-      <c r="AH12" s="5"/>
-      <c r="AI12" s="5"/>
-      <c r="AJ12" s="5"/>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="6"/>
+      <c r="AB12" s="6"/>
+      <c r="AC12" s="5"/>
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="5"/>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f t="shared" ref="A13:A15" si="9">A12</f>
         <v>DE00</v>
@@ -2015,27 +1854,14 @@
         <f t="array" ref="X13">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N13)*('COST(R)'!$B$2:$B$2731=$O13)*('COST(R)'!$C$2:$C$2731=$P13)*('COST(R)'!$E$2:$E$2731=$Q13)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>436.6230712505693</v>
       </c>
-      <c r="Z13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB13">
-        <v>2035</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD13" s="9"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="5"/>
-      <c r="AI13" s="5"/>
-      <c r="AJ13" s="5"/>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z13" s="6"/>
+      <c r="AA13" s="6"/>
+      <c r="AB13" s="6"/>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="5"/>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f t="shared" si="9"/>
         <v>DE00</v>
@@ -2118,27 +1944,14 @@
         <f t="array" ref="X14">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N14)*('COST(R)'!$B$2:$B$2731=$O14)*('COST(R)'!$C$2:$C$2731=$P14)*('COST(R)'!$E$2:$E$2731=$Q14)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>352.42672762472449</v>
       </c>
-      <c r="Z14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB14">
-        <v>2035</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD14" s="10"/>
-      <c r="AE14" s="6"/>
-      <c r="AF14" s="6"/>
-      <c r="AG14" s="6"/>
-      <c r="AH14" s="5"/>
-      <c r="AI14" s="5"/>
-      <c r="AJ14" s="5"/>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="5"/>
+      <c r="AD14" s="5"/>
+      <c r="AE14" s="5"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f t="shared" si="9"/>
         <v>DE00</v>
@@ -2221,27 +2034,14 @@
         <f t="array" ref="X15">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N15)*('COST(R)'!$B$2:$B$2731=$O15)*('COST(R)'!$C$2:$C$2731=$P15)*('COST(R)'!$E$2:$E$2731=$Q15)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>500.74820791711772</v>
       </c>
-      <c r="Z15" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB15">
-        <v>2035</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD15" s="9"/>
-      <c r="AE15" s="6"/>
-      <c r="AF15" s="6"/>
-      <c r="AG15" s="6"/>
-      <c r="AH15" s="5"/>
-      <c r="AI15" s="5"/>
-      <c r="AJ15" s="5"/>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="5"/>
+      <c r="AD15" s="5"/>
+      <c r="AE15" s="5"/>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -2322,27 +2122,14 @@
         <f t="array" ref="X16">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N16)*('COST(R)'!$B$2:$B$2731=$O16)*('COST(R)'!$C$2:$C$2731=$P16)*('COST(R)'!$E$2:$E$2731=$Q16)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>492.78199498925989</v>
       </c>
-      <c r="Z16" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB16">
-        <v>2040</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD16" s="9"/>
-      <c r="AE16" s="6"/>
-      <c r="AF16" s="6"/>
-      <c r="AG16" s="6"/>
-      <c r="AH16" s="5"/>
-      <c r="AI16" s="5"/>
-      <c r="AJ16" s="5"/>
-    </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z16" s="6"/>
+      <c r="AA16" s="6"/>
+      <c r="AB16" s="6"/>
+      <c r="AC16" s="5"/>
+      <c r="AD16" s="5"/>
+      <c r="AE16" s="5"/>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -2424,27 +2211,14 @@
         <f t="array" ref="X17">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N17)*('COST(R)'!$B$2:$B$2731=$O17)*('COST(R)'!$C$2:$C$2731=$P17)*('COST(R)'!$E$2:$E$2731=$Q17)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>517.1042451889582</v>
       </c>
-      <c r="Z17" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB17">
-        <v>2040</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD17" s="9"/>
-      <c r="AE17" s="6"/>
-      <c r="AF17" s="6"/>
-      <c r="AG17" s="6"/>
-      <c r="AH17" s="5"/>
-      <c r="AI17" s="5"/>
-      <c r="AJ17" s="5"/>
-    </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6"/>
+      <c r="AB17" s="6"/>
+      <c r="AC17" s="5"/>
+      <c r="AD17" s="5"/>
+      <c r="AE17" s="5"/>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>A17</f>
         <v>DKW1</v>
@@ -2527,27 +2301,14 @@
         <f t="array" ref="X18">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N18)*('COST(R)'!$B$2:$B$2731=$O18)*('COST(R)'!$C$2:$C$2731=$P18)*('COST(R)'!$E$2:$E$2731=$Q18)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>436.6230712505693</v>
       </c>
-      <c r="Z18" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB18">
-        <v>2040</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD18" s="10"/>
-      <c r="AE18" s="6"/>
-      <c r="AF18" s="6"/>
-      <c r="AG18" s="6"/>
-      <c r="AH18" s="5"/>
-      <c r="AI18" s="5"/>
-      <c r="AJ18" s="5"/>
-    </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="5"/>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="5"/>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f t="shared" ref="A19:A21" si="15">A18</f>
         <v>DKW1</v>
@@ -2630,27 +2391,14 @@
         <f t="array" ref="X19">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N19)*('COST(R)'!$B$2:$B$2731=$O19)*('COST(R)'!$C$2:$C$2731=$P19)*('COST(R)'!$E$2:$E$2731=$Q19)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>352.42672762472449</v>
       </c>
-      <c r="Z19" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB19">
-        <v>2040</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD19" s="9"/>
-      <c r="AE19" s="6"/>
-      <c r="AF19" s="6"/>
-      <c r="AG19" s="6"/>
-      <c r="AH19" s="5"/>
-      <c r="AI19" s="5"/>
-      <c r="AJ19" s="5"/>
-    </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="6"/>
+      <c r="AB19" s="6"/>
+      <c r="AC19" s="5"/>
+      <c r="AD19" s="5"/>
+      <c r="AE19" s="5"/>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f t="shared" si="15"/>
         <v>DKW1</v>
@@ -2733,27 +2481,14 @@
         <f t="array" ref="X20">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N20)*('COST(R)'!$B$2:$B$2731=$O20)*('COST(R)'!$C$2:$C$2731=$P20)*('COST(R)'!$E$2:$E$2731=$Q20)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>500.74820791711772</v>
       </c>
-      <c r="Z20" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB20">
-        <v>2040</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD20" s="10"/>
-      <c r="AE20" s="6"/>
-      <c r="AF20" s="6"/>
-      <c r="AG20" s="6"/>
-      <c r="AH20" s="5"/>
-      <c r="AI20" s="5"/>
-      <c r="AJ20" s="5"/>
-    </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="6"/>
+      <c r="AB20" s="6"/>
+      <c r="AC20" s="5"/>
+      <c r="AD20" s="5"/>
+      <c r="AE20" s="5"/>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f t="shared" si="15"/>
         <v>DKW1</v>
@@ -2836,27 +2571,14 @@
         <f t="array" ref="X21">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N21)*('COST(R)'!$B$2:$B$2731=$O21)*('COST(R)'!$C$2:$C$2731=$P21)*('COST(R)'!$E$2:$E$2731=$Q21)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>492.78199498925989</v>
       </c>
-      <c r="Z21" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB21">
-        <v>2040</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD21" s="9"/>
-      <c r="AE21" s="6"/>
-      <c r="AF21" s="6"/>
-      <c r="AG21" s="6"/>
-      <c r="AH21" s="5"/>
-      <c r="AI21" s="5"/>
-      <c r="AJ21" s="5"/>
-    </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z21" s="6"/>
+      <c r="AA21" s="6"/>
+      <c r="AB21" s="6"/>
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="5"/>
+      <c r="AE21" s="5"/>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -2937,27 +2659,14 @@
         <f t="array" ref="X22">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N22)*('COST(R)'!$B$2:$B$2731=$O22)*('COST(R)'!$C$2:$C$2731=$P22)*('COST(R)'!$E$2:$E$2731=$Q22)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>517.1042451889582</v>
       </c>
-      <c r="Z22" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB22">
-        <v>2045</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD22" s="9"/>
-      <c r="AE22" s="6"/>
-      <c r="AF22" s="6"/>
-      <c r="AG22" s="6"/>
-      <c r="AH22" s="5"/>
-      <c r="AI22" s="5"/>
-      <c r="AJ22" s="5"/>
-    </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="6"/>
+      <c r="AB22" s="6"/>
+      <c r="AC22" s="5"/>
+      <c r="AD22" s="5"/>
+      <c r="AE22" s="5"/>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>61</v>
       </c>
@@ -3039,27 +2748,14 @@
         <f t="array" ref="X23">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N23)*('COST(R)'!$B$2:$B$2731=$O23)*('COST(R)'!$C$2:$C$2731=$P23)*('COST(R)'!$E$2:$E$2731=$Q23)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>436.6230712505693</v>
       </c>
-      <c r="Z23" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB23">
-        <v>2045</v>
-      </c>
-      <c r="AC23" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD23" s="9"/>
-      <c r="AE23" s="6"/>
-      <c r="AF23" s="6"/>
-      <c r="AG23" s="6"/>
-      <c r="AH23" s="5"/>
-      <c r="AI23" s="5"/>
-      <c r="AJ23" s="5"/>
-    </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="6"/>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="5"/>
+      <c r="AD23" s="5"/>
+      <c r="AE23" s="5"/>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>A23</f>
         <v>NL00</v>
@@ -3142,27 +2838,14 @@
         <f t="array" ref="X24">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N24)*('COST(R)'!$B$2:$B$2731=$O24)*('COST(R)'!$C$2:$C$2731=$P24)*('COST(R)'!$E$2:$E$2731=$Q24)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>352.42672762472449</v>
       </c>
-      <c r="Z24" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB24">
-        <v>2045</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD24" s="10"/>
-      <c r="AE24" s="6"/>
-      <c r="AF24" s="6"/>
-      <c r="AG24" s="6"/>
-      <c r="AH24" s="5"/>
-      <c r="AI24" s="5"/>
-      <c r="AJ24" s="5"/>
-    </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z24" s="6"/>
+      <c r="AA24" s="6"/>
+      <c r="AB24" s="6"/>
+      <c r="AC24" s="5"/>
+      <c r="AD24" s="5"/>
+      <c r="AE24" s="5"/>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f t="shared" ref="A25:A27" si="21">A24</f>
         <v>NL00</v>
@@ -3245,27 +2928,14 @@
         <f t="array" ref="X25">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N25)*('COST(R)'!$B$2:$B$2731=$O25)*('COST(R)'!$C$2:$C$2731=$P25)*('COST(R)'!$E$2:$E$2731=$Q25)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>500.74820791711772</v>
       </c>
-      <c r="Z25" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB25">
-        <v>2045</v>
-      </c>
-      <c r="AC25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD25" s="9"/>
-      <c r="AE25" s="6"/>
-      <c r="AF25" s="6"/>
-      <c r="AG25" s="6"/>
-      <c r="AH25" s="5"/>
-      <c r="AI25" s="5"/>
-      <c r="AJ25" s="5"/>
-    </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z25" s="6"/>
+      <c r="AA25" s="6"/>
+      <c r="AB25" s="6"/>
+      <c r="AC25" s="5"/>
+      <c r="AD25" s="5"/>
+      <c r="AE25" s="5"/>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f t="shared" si="21"/>
         <v>NL00</v>
@@ -3348,27 +3018,14 @@
         <f t="array" ref="X26">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N26)*('COST(R)'!$B$2:$B$2731=$O26)*('COST(R)'!$C$2:$C$2731=$P26)*('COST(R)'!$E$2:$E$2731=$Q26)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>492.78199498925989</v>
       </c>
-      <c r="Z26" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB26">
-        <v>2045</v>
-      </c>
-      <c r="AC26" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD26" s="10"/>
-      <c r="AE26" s="6"/>
-      <c r="AF26" s="6"/>
-      <c r="AG26" s="6"/>
-      <c r="AH26" s="5"/>
-      <c r="AI26" s="5"/>
-      <c r="AJ26" s="5"/>
-    </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z26" s="6"/>
+      <c r="AA26" s="6"/>
+      <c r="AB26" s="6"/>
+      <c r="AC26" s="5"/>
+      <c r="AD26" s="5"/>
+      <c r="AE26" s="5"/>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f t="shared" si="21"/>
         <v>NL00</v>
@@ -3451,27 +3108,14 @@
         <f t="array" ref="X27">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N27)*('COST(R)'!$B$2:$B$2731=$O27)*('COST(R)'!$C$2:$C$2731=$P27)*('COST(R)'!$E$2:$E$2731=$Q27)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>517.1042451889582</v>
       </c>
-      <c r="Z27" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA27" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB27">
-        <v>2045</v>
-      </c>
-      <c r="AC27" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD27" s="9"/>
-      <c r="AE27" s="6"/>
-      <c r="AF27" s="6"/>
-      <c r="AG27" s="6"/>
-      <c r="AH27" s="5"/>
-      <c r="AI27" s="5"/>
-      <c r="AJ27" s="5"/>
-    </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z27" s="6"/>
+      <c r="AA27" s="6"/>
+      <c r="AB27" s="6"/>
+      <c r="AC27" s="5"/>
+      <c r="AD27" s="5"/>
+      <c r="AE27" s="5"/>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -3551,27 +3195,14 @@
         <f t="array" ref="X28">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N28)*('COST(R)'!$B$2:$B$2731=$O28)*('COST(R)'!$C$2:$C$2731=$P28)*('COST(R)'!$E$2:$E$2731=$Q28)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>436.6230712505693</v>
       </c>
-      <c r="Z28" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB28">
-        <v>2050</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD28" s="9"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="5"/>
-      <c r="AI28" s="5"/>
-      <c r="AJ28" s="5"/>
-    </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z28" s="6"/>
+      <c r="AA28" s="6"/>
+      <c r="AB28" s="6"/>
+      <c r="AC28" s="5"/>
+      <c r="AD28" s="5"/>
+      <c r="AE28" s="5"/>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>66</v>
       </c>
@@ -3614,27 +3245,14 @@
         <f t="array" ref="K29">SUM(($S$4:$X$28)*($P$4:$P$28=$C29)*($O$4:$O$28=$A29)*($S$3:$X$3=K$3)*($S$2:$X$2=K$2))</f>
         <v>436.6230712505693</v>
       </c>
-      <c r="Z29" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB29">
-        <v>2050</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD29" s="9"/>
-      <c r="AE29" s="6"/>
-      <c r="AF29" s="6"/>
-      <c r="AG29" s="6"/>
-      <c r="AH29" s="5"/>
-      <c r="AI29" s="5"/>
-      <c r="AJ29" s="5"/>
-    </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z29" s="6"/>
+      <c r="AA29" s="6"/>
+      <c r="AB29" s="6"/>
+      <c r="AC29" s="5"/>
+      <c r="AD29" s="5"/>
+      <c r="AE29" s="5"/>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>A29</f>
         <v>NOS0</v>
@@ -3717,27 +3335,14 @@
         <f t="array" ref="X30">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N30)*('COST(R)'!$B$2:$B$2731=$O30)*('COST(R)'!$C$2:$C$2731=$P30)*('COST(R)'!$E$2:$E$2731=$Q30)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>0</v>
       </c>
-      <c r="Z30" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB30">
-        <v>2050</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD30" s="10"/>
-      <c r="AE30" s="6"/>
-      <c r="AF30" s="6"/>
-      <c r="AG30" s="6"/>
-      <c r="AH30" s="5"/>
-      <c r="AI30" s="5"/>
-      <c r="AJ30" s="5"/>
-    </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z30" s="6"/>
+      <c r="AA30" s="6"/>
+      <c r="AB30" s="6"/>
+      <c r="AC30" s="5"/>
+      <c r="AD30" s="5"/>
+      <c r="AE30" s="5"/>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f t="shared" ref="A31:A33" si="27">A30</f>
         <v>NOS0</v>
@@ -3820,27 +3425,14 @@
         <f t="array" ref="X31">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N31)*('COST(R)'!$B$2:$B$2731=$O31)*('COST(R)'!$C$2:$C$2731=$P31)*('COST(R)'!$E$2:$E$2731=$Q31)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>0</v>
       </c>
-      <c r="Z31" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB31">
-        <v>2050</v>
-      </c>
-      <c r="AC31" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD31" s="9"/>
-      <c r="AE31" s="6"/>
-      <c r="AF31" s="6"/>
-      <c r="AG31" s="6"/>
-      <c r="AH31" s="5"/>
-      <c r="AI31" s="5"/>
-      <c r="AJ31" s="5"/>
-    </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z31" s="6"/>
+      <c r="AA31" s="6"/>
+      <c r="AB31" s="6"/>
+      <c r="AC31" s="5"/>
+      <c r="AD31" s="5"/>
+      <c r="AE31" s="5"/>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f t="shared" si="27"/>
         <v>NOS0</v>
@@ -3923,27 +3515,14 @@
         <f t="array" ref="X32">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N32)*('COST(R)'!$B$2:$B$2731=$O32)*('COST(R)'!$C$2:$C$2731=$P32)*('COST(R)'!$E$2:$E$2731=$Q32)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>0</v>
       </c>
-      <c r="Z32" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB32">
-        <v>2050</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD32" s="10"/>
-      <c r="AE32" s="6"/>
-      <c r="AF32" s="6"/>
-      <c r="AG32" s="6"/>
-      <c r="AH32" s="5"/>
-      <c r="AI32" s="5"/>
-      <c r="AJ32" s="5"/>
-    </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="6"/>
+      <c r="AB32" s="6"/>
+      <c r="AC32" s="5"/>
+      <c r="AD32" s="5"/>
+      <c r="AE32" s="5"/>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f t="shared" si="27"/>
         <v>NOS0</v>
@@ -4026,27 +3605,14 @@
         <f t="array" ref="X33">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N33)*('COST(R)'!$B$2:$B$2731=$O33)*('COST(R)'!$C$2:$C$2731=$P33)*('COST(R)'!$E$2:$E$2731=$Q33)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>0</v>
       </c>
-      <c r="Z33" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA33" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB33">
-        <v>2050</v>
-      </c>
-      <c r="AC33" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD33" s="9"/>
-      <c r="AE33" s="6"/>
-      <c r="AF33" s="6"/>
-      <c r="AG33" s="6"/>
-      <c r="AH33" s="5"/>
-      <c r="AI33" s="5"/>
-      <c r="AJ33" s="5"/>
-    </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="Z33" s="6"/>
+      <c r="AA33" s="6"/>
+      <c r="AB33" s="6"/>
+      <c r="AC33" s="5"/>
+      <c r="AD33" s="5"/>
+      <c r="AE33" s="5"/>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -4128,7 +3694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -4210,9 +3776,8 @@
         <f t="array" ref="X35">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N35)*('COST(R)'!$B$2:$B$2731=$O35)*('COST(R)'!$C$2:$C$2731=$P35)*('COST(R)'!$E$2:$E$2731=$Q35)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>0</v>
       </c>
-      <c r="AD35" s="9"/>
-    </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f>A35</f>
         <v>UK00</v>
@@ -4295,9 +3860,8 @@
         <f t="array" ref="X36">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N36)*('COST(R)'!$B$2:$B$2731=$O36)*('COST(R)'!$C$2:$C$2731=$P36)*('COST(R)'!$E$2:$E$2731=$Q36)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>0</v>
       </c>
-      <c r="AD36" s="9"/>
-    </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f t="shared" ref="A37:A39" si="35">A36</f>
         <v>UK00</v>
@@ -4380,9 +3944,8 @@
         <f t="array" ref="X37">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N37)*('COST(R)'!$B$2:$B$2731=$O37)*('COST(R)'!$C$2:$C$2731=$P37)*('COST(R)'!$E$2:$E$2731=$Q37)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>0</v>
       </c>
-      <c r="AD37" s="10"/>
-    </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f t="shared" si="35"/>
         <v>UK00</v>
@@ -4465,9 +4028,8 @@
         <f t="array" ref="X38">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N38)*('COST(R)'!$B$2:$B$2731=$O38)*('COST(R)'!$C$2:$C$2731=$P38)*('COST(R)'!$E$2:$E$2731=$Q38)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>0</v>
       </c>
-      <c r="AD38" s="9"/>
-    </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f t="shared" si="35"/>
         <v>UK00</v>
@@ -4550,9 +4112,8 @@
         <f t="array" ref="X39">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N39)*('COST(R)'!$B$2:$B$2731=$O39)*('COST(R)'!$C$2:$C$2731=$P39)*('COST(R)'!$E$2:$E$2731=$Q39)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>0</v>
       </c>
-      <c r="AD39" s="10"/>
-    </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="N40" s="13" t="s">
         <v>25</v>
       </c>
@@ -4592,9 +4153,8 @@
         <f t="array" ref="X40">SUM('COST(R)'!$F$2:$G$2731*('COST(R)'!$A$2:$A$2731=$N40)*('COST(R)'!$B$2:$B$2731=$O40)*('COST(R)'!$C$2:$C$2731=$P40)*('COST(R)'!$E$2:$E$2731=$Q40)*('COST(R)'!$D$2:$D$2731=X$2)*('COST(R)'!$F$1:$G$1=X$3))</f>
         <v>580.59554555666955</v>
       </c>
-      <c r="AD40" s="9"/>
-    </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="N41" s="13" t="s">
         <v>25</v>
       </c>
@@ -4635,7 +4195,7 @@
         <v>580.59554555666955</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="N42" s="13" t="s">
         <v>25</v>
       </c>
@@ -4676,7 +4236,7 @@
         <v>580.59554555666955</v>
       </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="N43" s="13" t="s">
         <v>25</v>
       </c>
@@ -4717,7 +4277,7 @@
         <v>580.59554555666955</v>
       </c>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="N44" s="13" t="s">
         <v>25</v>
       </c>
@@ -4758,7 +4318,7 @@
         <v>580.59554555666955</v>
       </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
       <c r="N45" t="s">
         <v>77</v>
       </c>
@@ -4799,7 +4359,7 @@
         <v>569.67884401760523</v>
       </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
       <c r="N46" t="s">
         <v>77</v>
       </c>
@@ -4840,7 +4400,7 @@
         <v>569.67884401760523</v>
       </c>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
       <c r="N47" t="s">
         <v>77</v>
       </c>
@@ -4881,7 +4441,7 @@
         <v>569.67884401760523</v>
       </c>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="N48" t="s">
         <v>77</v>
       </c>
@@ -5374,9 +4934,6 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="Z4:AB33">
-    <sortCondition ref="AB4:AB33"/>
-  </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -57212,7 +56769,7 @@
         <v>0.33928198183868402</v>
       </c>
     </row>
-    <row r="2254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2254" t="s">
         <v>25</v>
       </c>
@@ -57304,7 +56861,7 @@
         <v>0.33928198183868402</v>
       </c>
     </row>
-    <row r="2258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2258" t="s">
         <v>25</v>
       </c>
@@ -57442,7 +56999,7 @@
         <v>0.33928198183868402</v>
       </c>
     </row>
-    <row r="2264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2264" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2264" t="s">
         <v>25</v>
       </c>
@@ -57534,7 +57091,7 @@
         <v>0.33928198183868402</v>
       </c>
     </row>
-    <row r="2268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2268" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2268" t="s">
         <v>25</v>
       </c>
@@ -57672,7 +57229,7 @@
         <v>0.33928198183868402</v>
       </c>
     </row>
-    <row r="2274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2274" t="s">
         <v>25</v>
       </c>
@@ -57764,7 +57321,7 @@
         <v>0.33928198183868402</v>
       </c>
     </row>
-    <row r="2278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2278" t="s">
         <v>25</v>
       </c>
@@ -60662,7 +60219,7 @@
         <v>0.32807844270122088</v>
       </c>
     </row>
-    <row r="2404" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2404" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2404" t="s">
         <v>77</v>
       </c>
@@ -60754,7 +60311,7 @@
         <v>0.32807844270122088</v>
       </c>
     </row>
-    <row r="2408" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2408" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2408" t="s">
         <v>77</v>
       </c>
@@ -60892,7 +60449,7 @@
         <v>0.32807844270122088</v>
       </c>
     </row>
-    <row r="2414" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2414" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2414" t="s">
         <v>77</v>
       </c>
@@ -60984,7 +60541,7 @@
         <v>0.32807844270122088</v>
       </c>
     </row>
-    <row r="2418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2418" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2418" t="s">
         <v>77</v>
       </c>
@@ -61122,7 +60679,7 @@
         <v>0.32807844270122088</v>
       </c>
     </row>
-    <row r="2424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2424" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2424" t="s">
         <v>77</v>
       </c>
@@ -61214,7 +60771,7 @@
         <v>0.32807844270122088</v>
       </c>
     </row>
-    <row r="2428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2428" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2428" t="s">
         <v>77</v>
       </c>
@@ -62042,7 +61599,7 @@
         <v>7.9263354825464136E-2</v>
       </c>
     </row>
-    <row r="2464" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2464" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2464" t="s">
         <v>20</v>
       </c>
@@ -62134,7 +61691,7 @@
         <v>7.9263354825464136E-2</v>
       </c>
     </row>
-    <row r="2468" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2468" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2468" t="s">
         <v>20</v>
       </c>
@@ -62272,7 +61829,7 @@
         <v>7.9263354825464136E-2</v>
       </c>
     </row>
-    <row r="2474" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2474" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2474" t="s">
         <v>20</v>
       </c>
@@ -62364,7 +61921,7 @@
         <v>7.9263354825464136E-2</v>
       </c>
     </row>
-    <row r="2478" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2478" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2478" t="s">
         <v>20</v>
       </c>
@@ -62502,7 +62059,7 @@
         <v>7.9263354825464136E-2</v>
       </c>
     </row>
-    <row r="2484" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2484" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2484" t="s">
         <v>20</v>
       </c>
@@ -62594,7 +62151,7 @@
         <v>7.9263354825464136E-2</v>
       </c>
     </row>
-    <row r="2488" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2488" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2488" t="s">
         <v>20</v>
       </c>
@@ -67562,7 +67119,7 @@
         <v>7.9147000836455914E-2</v>
       </c>
     </row>
-    <row r="2704" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2704" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2704" t="s">
         <v>68</v>
       </c>
@@ -67654,7 +67211,7 @@
         <v>7.9147000836455914E-2</v>
       </c>
     </row>
-    <row r="2708" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2708" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2708" t="s">
         <v>68</v>
       </c>
@@ -67792,7 +67349,7 @@
         <v>7.9147000836455914E-2</v>
       </c>
     </row>
-    <row r="2714" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2714" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2714" t="s">
         <v>68</v>
       </c>
@@ -67884,7 +67441,7 @@
         <v>7.9147000836455914E-2</v>
       </c>
     </row>
-    <row r="2718" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2718" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2718" t="s">
         <v>68</v>
       </c>
@@ -68022,7 +67579,7 @@
         <v>7.9147000836455914E-2</v>
       </c>
     </row>
-    <row r="2724" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2724" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2724" t="s">
         <v>68</v>
       </c>
@@ -68114,7 +67671,7 @@
         <v>7.9147000836455914E-2</v>
       </c>
     </row>
-    <row r="2728" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2728" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2728" t="s">
         <v>68</v>
       </c>
@@ -68219,6 +67776,13 @@
     <filterColumn colId="1">
       <filters>
         <filter val="UK00"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="2030"/>
+        <filter val="2040"/>
+        <filter val="2050"/>
       </filters>
     </filterColumn>
     <filterColumn colId="4">
@@ -68745,7 +68309,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -68765,7 +68329,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -68805,7 +68369,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -68945,7 +68509,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -68965,7 +68529,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -69105,7 +68669,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>24</v>
       </c>
@@ -69125,7 +68689,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -69670,7 +69234,7 @@
       <c r="T71" s="2"/>
       <c r="U71" s="2"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -69690,7 +69254,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>21</v>
       </c>
@@ -69730,7 +69294,7 @@
         <v>3134.125</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>23</v>
       </c>
@@ -69870,7 +69434,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>17</v>
       </c>
@@ -69890,7 +69454,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>24</v>
       </c>
@@ -70030,7 +69594,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>24</v>
       </c>
@@ -70050,7 +69614,7 @@
         <v>7300</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>27</v>
       </c>
@@ -70591,6 +70155,13 @@
         <filter val="UK00"/>
       </filters>
     </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="2030"/>
+        <filter val="2040"/>
+        <filter val="2050"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -70603,58 +70174,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="e3fb2008-9808-4f29-aa32-2f66631018ed">
-      <Value>3</Value>
-      <Value>2</Value>
-      <Value>1</Value>
-    </TaxCatchAll>
-    <MYENTSOE_SiteType xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">MYENTSOE</MYENTSOE_SiteType>
-    <o7c6620afba5434aaae6ef9be3dfdbd2 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Extranet</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">922fc1ba-0c8d-4fbf-b30d-83722d0f30f2</TermId>
-        </TermInfo>
-      </Terms>
-    </o7c6620afba5434aaae6ef9be3dfdbd2>
-    <h9003f7b9f494612977846e0050fed71 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">SDC</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">414c202c-9255-45c1-8290-a69e6acf8153</TermId>
-        </TermInfo>
-      </Terms>
-    </h9003f7b9f494612977846e0050fed71>
-    <pbc0f0de950a4a35a97ec71d1ea28ac6 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </pbc0f0de950a4a35a97ec71d1ea28ac6>
-    <cd67ed8a84074a6585f4dff49f8697b2 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </cd67ed8a84074a6585f4dff49f8697b2>
-    <ka6aaa3f9c694727892a9d4c842b0cb7 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ka6aaa3f9c694727892a9d4c842b0cb7>
-    <ff9ab3467cf04ce9aa1cff0f5f816655 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Shared</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">04da8cfa-2b68-4725-9db5-e7b66ab623e6</TermId>
-        </TermInfo>
-      </Terms>
-    </ff9ab3467cf04ce9aa1cff0f5f816655>
-    <h00809838d2c4acabc9e4b8e74fa1ba3 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </h00809838d2c4acabc9e4b8e74fa1ba3>
-    <f25aee4750b24120b97bdbb6766dd771 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </f25aee4750b24120b97bdbb6766dd771>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007A5B6B50967DEB4BA6EFC3DC4B3E4C2D" ma:contentTypeVersion="25" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f1f9003c72b0ce3e143193d073f3d1a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9b216c6c-829b-4bd6-a7b8-61d756915eca" xmlns:ns3="e3fb2008-9808-4f29-aa32-2f66631018ed" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c4b0a95e95378f5f31da9657be19360d" ns2:_="" ns3:_="">
     <xsd:import namespace="9b216c6c-829b-4bd6-a7b8-61d756915eca"/>
@@ -70885,6 +70404,58 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="e3fb2008-9808-4f29-aa32-2f66631018ed">
+      <Value>3</Value>
+      <Value>2</Value>
+      <Value>1</Value>
+    </TaxCatchAll>
+    <MYENTSOE_SiteType xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">MYENTSOE</MYENTSOE_SiteType>
+    <o7c6620afba5434aaae6ef9be3dfdbd2 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Extranet</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">922fc1ba-0c8d-4fbf-b30d-83722d0f30f2</TermId>
+        </TermInfo>
+      </Terms>
+    </o7c6620afba5434aaae6ef9be3dfdbd2>
+    <h9003f7b9f494612977846e0050fed71 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">SDC</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">414c202c-9255-45c1-8290-a69e6acf8153</TermId>
+        </TermInfo>
+      </Terms>
+    </h9003f7b9f494612977846e0050fed71>
+    <pbc0f0de950a4a35a97ec71d1ea28ac6 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </pbc0f0de950a4a35a97ec71d1ea28ac6>
+    <cd67ed8a84074a6585f4dff49f8697b2 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </cd67ed8a84074a6585f4dff49f8697b2>
+    <ka6aaa3f9c694727892a9d4c842b0cb7 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ka6aaa3f9c694727892a9d4c842b0cb7>
+    <ff9ab3467cf04ce9aa1cff0f5f816655 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Shared</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">04da8cfa-2b68-4725-9db5-e7b66ab623e6</TermId>
+        </TermInfo>
+      </Terms>
+    </ff9ab3467cf04ce9aa1cff0f5f816655>
+    <h00809838d2c4acabc9e4b8e74fa1ba3 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </h00809838d2c4acabc9e4b8e74fa1ba3>
+    <f25aee4750b24120b97bdbb6766dd771 xmlns="9b216c6c-829b-4bd6-a7b8-61d756915eca">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </f25aee4750b24120b97bdbb6766dd771>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE16E379-A634-41B3-B5D2-5DF52FCA68E4}">
   <ds:schemaRefs>
@@ -70894,17 +70465,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED061371-D0A3-44B6-BFC5-DC16BE680E8E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="e3fb2008-9808-4f29-aa32-2f66631018ed"/>
-    <ds:schemaRef ds:uri="9b216c6c-829b-4bd6-a7b8-61d756915eca"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8CCAC78-3954-4FCC-A29B-C3164C7C3E66}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -70921,4 +70481,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED061371-D0A3-44B6-BFC5-DC16BE680E8E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e3fb2008-9808-4f29-aa32-2f66631018ed"/>
+    <ds:schemaRef ds:uri="9b216c6c-829b-4bd6-a7b8-61d756915eca"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>